--- a/artfynd/A 61806-2023 artfynd.xlsx
+++ b/artfynd/A 61806-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 61806-2023 artfynd.xlsx
+++ b/artfynd/A 61806-2023 artfynd.xlsx
@@ -773,7 +773,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">

--- a/artfynd/A 61806-2023 artfynd.xlsx
+++ b/artfynd/A 61806-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>113618452</v>
       </c>
       <c r="B2" t="n">
-        <v>90594</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92205</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
